--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>275.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>275</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>200</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>200</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>12/09 16:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>175</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>175</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>175</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>150</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>150</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>12/09 16:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>140</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>150</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>140</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>150</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>140</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>125</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>125</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>125</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>125</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>110</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>125</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>13/09 16:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>110</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>125</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>12/09 22:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>80.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>80</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,187 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45912.06129546242</v>
+        <v>45912.06129546296</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | FTC-Teleko</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FTC-Telekom – EC VSVAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>12/09 16:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+162%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45912.12250305909</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | SaiPa – Ko</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SaiPa – KooKooFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>12/09 15:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+102%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45912.12250305909</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lugano – Z</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Lugano – ZugSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+94,9%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45912.12250305909</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Djurgården</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Djurgårdens IF – Skellefteå AIKSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>13/09 13:15</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+63,8%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45912.12250305909</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -1580,10 +1580,8 @@
           <t>12/09 16:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>175</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45912.12250305909</v>
+        <v>45912.12250305556</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>150</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45912.12250305909</v>
+        <v>45912.12250305556</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>125</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45912.12250305909</v>
+        <v>45912.12250305556</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>110</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45912.12250305909</v>
+        <v>45912.12250305556</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1726,6 +1726,141 @@
         <v>45912.12250305556</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Nuremberg </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Nuremberg Ice Tigers – AugsbourgDEL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>12/09 17:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+167%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45912.1836290517</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Presov – P</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Presov – PopradSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>12/09 16:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+163%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45912.1836290517</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kärpät Oul</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Kärpät Oulu – Ilves TampereFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>12/09 15:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+61,8%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45912.1836290517</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>200</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45912.1836290517</v>
+        <v>45912.18362905092</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>200</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45912.1836290517</v>
+        <v>45912.18362905092</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>110</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,52 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45912.1836290517</v>
+        <v>45912.18362905092</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Banska Bys</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Banska Bystrica – ZvolenSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>12/09 15:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+113%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45912.22164215083</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,23 +1881,201 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>175</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+113%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45912.22164215278</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Bolzano – </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bolzano – RB SalzbourgICE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>+113%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>45912.22164215083</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+167%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45912.27192101863</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Vitkovi</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HC Vitkovice – HC Rytiri KladnoExtraliga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>12/09 15:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+102%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45912.27192101863</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lowen Fran</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Lowen Frankfurt – Grizzlys WolfsburgDEL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>12/09 17:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+101%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45912.27192101863</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Cologne Ha</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Cologne Haie – EHC MunichDEL - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>12/09 17:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+65,7%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45912.27192101863</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>175</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45912.27192101863</v>
+        <v>45912.27192101852</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>140</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45912.27192101863</v>
+        <v>45912.27192101852</v>
       </c>
     </row>
     <row r="37">
@@ -2014,10 +2010,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>140</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2030,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45912.27192101863</v>
+        <v>45912.27192101852</v>
       </c>
     </row>
     <row r="38">
@@ -2059,23 +2053,66 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>110</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+65,7%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45912.27192101852</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | SC Bern – </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SC Bern – Genève-ServetteNational League A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>110.00</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>+65,7%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>45912.27192101863</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+80,1%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45912.30524552416</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,23 +2096,561 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>110</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+80,1%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45912.30524552083</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ingolstadt</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ingolstadt – Iserlohn RoostersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>12/09 17:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+136%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45912.35260615484</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Zug – Lang</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Zug – Langnau TigersSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>13/09 17:45</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+111%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45912.35260615484</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | SC Rappers</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SC Rapperswil-Jona Lakers – SC BernNational League A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>13/09 17:45</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+93,1%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45912.35260615484</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ambri Piot</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ambri Piotta – LausanneSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>13/09 17:45</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+81,6%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45912.35260615484</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Adler Mann</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Adler Mannheim – Straubing TigersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>12/09 17:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+77,4%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45912.35260615484</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Langnau Ti</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Langnau Tigers – Ambri PiottaSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>99.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+64,7%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45912.35260615484</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Hockey | Pas de buts | SC Bern – </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SC Bern – Servette GESuisse - NLA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+64,2%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45912.35260615484</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lausanne –</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Lausanne – Fribourg GotteronSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>98.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+62,7%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45912.35260615484</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Genève-Ser</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Genève-Servette – Kloten FlyersSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>13/09 17:45</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>110.00</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>+80,1%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>45912.30524552416</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+60,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45912.35260615484</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | S.Bratisla</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>S.Bratislava – HC KosiceSlovaquie - Extraliga</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>12/09 16:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+58,2%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45912.35260615484</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | HK Olimpij</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HK Olimpija Ljubljana – Vienne CapitalsAutriche - ICE Hockey League</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+56,0%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45912.35260615484</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KAC – Fehe</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>KAC – Fehervar AV19Autriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>97.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+55,3%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45912.35260615484</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>175</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45912.35260615484</v>
+        <v>45912.35260615741</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>13/09 17:45</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>140</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45912.35260615484</v>
+        <v>45912.35260615741</v>
       </c>
     </row>
     <row r="42">
@@ -2229,10 +2225,8 @@
           <t>13/09 17:45</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>140</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2245,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45912.35260615484</v>
+        <v>45912.35260615741</v>
       </c>
     </row>
     <row r="43">
@@ -2274,10 +2268,8 @@
           <t>13/09 17:45</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>125</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2290,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45912.35260615484</v>
+        <v>45912.35260615741</v>
       </c>
     </row>
     <row r="44">
@@ -2319,10 +2311,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>125</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2335,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45912.35260615484</v>
+        <v>45912.35260615741</v>
       </c>
     </row>
     <row r="45">
@@ -2364,10 +2354,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2380,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45912.35260615484</v>
+        <v>45912.35260615741</v>
       </c>
     </row>
     <row r="46">
@@ -2409,10 +2397,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>100</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2425,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45912.35260615484</v>
+        <v>45912.35260615741</v>
       </c>
     </row>
     <row r="47">
@@ -2454,10 +2440,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>98.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>98</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2470,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45912.35260615484</v>
+        <v>45912.35260615741</v>
       </c>
     </row>
     <row r="48">
@@ -2499,10 +2483,8 @@
           <t>13/09 17:45</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>110</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2515,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45912.35260615484</v>
+        <v>45912.35260615741</v>
       </c>
     </row>
     <row r="49">
@@ -2544,10 +2526,8 @@
           <t>12/09 16:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>100</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2560,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45912.35260615484</v>
+        <v>45912.35260615741</v>
       </c>
     </row>
     <row r="50">
@@ -2589,10 +2569,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>101</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2605,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45912.35260615484</v>
+        <v>45912.35260615741</v>
       </c>
     </row>
     <row r="51">
@@ -2634,10 +2612,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>97.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>97</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2650,7 +2626,142 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45912.35260615484</v>
+        <v>45912.35260615741</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Ambri P</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HC Ambri Piotta – LausanneNational League A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>13/09 17:45</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+78,2%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45912.38955679495</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Ajoie P</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HC Ajoie Porrentruy – ZSC LionsNational League A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+74,9%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45912.38955679495</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Olimpija L</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Olimpija Ljubljana – Spusu Vienna CapitalsICE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+74,4%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45912.38955679495</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>13/09 17:45</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>125</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45912.38955679495</v>
+        <v>45912.38955679398</v>
       </c>
     </row>
     <row r="53">
@@ -2700,10 +2698,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>110</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2716,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45912.38955679495</v>
+        <v>45912.38955679398</v>
       </c>
     </row>
     <row r="54">
@@ -2745,10 +2741,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>110</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2761,7 +2755,142 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45912.38955679495</v>
+        <v>45912.38955679398</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Fischtown </t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fischtown Pinguins – Wild WingsDEL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>12/09 17:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+119%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45912.43179584423</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Rapperswil</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Rapperswil Jona Lakers – BernSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>13/09 17:45</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+106%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45912.43179584423</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EV Zug – S</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EV Zug – SCL TigersNational League A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>13/09 17:45</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+83,7%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45912.43179584423</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>150</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45912.43179584423</v>
+        <v>45912.43179584491</v>
       </c>
     </row>
     <row r="56">
@@ -2829,10 +2827,8 @@
           <t>13/09 17:45</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>140</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2845,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45912.43179584423</v>
+        <v>45912.43179584491</v>
       </c>
     </row>
     <row r="57">
@@ -2874,10 +2870,8 @@
           <t>13/09 17:45</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>125</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2890,7 +2884,52 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45912.43179584423</v>
+        <v>45912.43179584491</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Bili Tygri</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Bili Tygri Liberec – HC PardubiceExtraliga</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>12/09 16:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+84,5%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45912.47019498321</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,10 +2913,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>110</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,52 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45912.47019498321</v>
+        <v>45912.47019498843</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Twk Inn</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HC Twk Innsbruck Die Haie – Pustertal WolfeICE</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+165%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45912.52829882393</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>175</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,52 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45912.52829882393</v>
+        <v>45912.52829881944</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Moins que 0.5 | Olomouc – </t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Olomouc – PlzenRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>12/09 16:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>87.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,30%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45912.56097057871</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2999,10 +2999,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>87.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>87</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3016,6 +3014,51 @@
       </c>
       <c r="I60" s="2" t="n">
         <v>45912.56097057871</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Davos – Aj</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Davos – AjoieSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>14/09 13:45</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+114%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45912.59704506092</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>14/09 13:45</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>140</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,52 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45912.59704506092</v>
+        <v>45912.59704505787</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – HC KosiceExtraliga A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>12/09 16:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+89,2%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45912.63902278682</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,23 +3085,201 @@
           <t>12/09 16:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="n">
+        <v>125</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+89,2%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45912.63902278935</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | KAC Klagen</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>KAC Klagenfurt – Fehervar AV19ICE</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+77,3%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45912.68201499711</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kölner Hai</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Kölner Haie – MunichAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>12/09 17:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>+89,2%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>45912.63902278682</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+75,9%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45912.68201499711</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | ZSC Lions </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ZSC Lions – LuganoSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>13/09 17:45</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+70,7%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45912.68201499711</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Fribourg G</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Fribourg Gotteron – EHC Biel-BienneSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>13/09 17:45</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+60,4%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45912.68201499711</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>110</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45912.68201499711</v>
+        <v>45912.682015</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>125</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45912.68201499711</v>
+        <v>45912.682015</v>
       </c>
     </row>
     <row r="65">
@@ -3218,10 +3214,8 @@
           <t>13/09 17:45</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>110</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3234,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45912.68201499711</v>
+        <v>45912.682015</v>
       </c>
     </row>
     <row r="66">
@@ -3263,23 +3257,201 @@
           <t>13/09 17:45</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" t="n">
+        <v>100</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+60,4%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45912.682015</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kloten Fly</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Kloten Flyers – Rapperswil Jona LakersSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>98.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+55,2%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45912.72053087192</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | Severstal </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Severstal Tcherepovets – CSKA MoscouRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+52,1%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45912.72053087192</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | HV71 – Ore</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HV71 – Orebro HKSuede - SHL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>13/09 16:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>95.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+48,7%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45912.72053087192</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Frölunda H</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Frölunda HC – Linköpings HCSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>13/09 13:15</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>1,60%</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>+60,4%</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>45912.68201499711</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+46,3%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45912.72053087192</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,10 +3300,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>98.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>98</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3316,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45912.72053087192</v>
+        <v>45912.72053086806</v>
       </c>
     </row>
     <row r="68">
@@ -3345,10 +3343,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>101</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3361,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45912.72053087192</v>
+        <v>45912.72053086806</v>
       </c>
     </row>
     <row r="69">
@@ -3390,10 +3386,8 @@
           <t>13/09 16:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>95.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>95</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3406,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45912.72053087192</v>
+        <v>45912.72053086806</v>
       </c>
     </row>
     <row r="70">
@@ -3435,23 +3429,606 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" t="n">
+        <v>100</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+46,3%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45912.72053086806</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Brynäs IF </t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Brynäs IF – Växjö Lakers HCSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>13/09 13:15</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>+46,3%</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>45912.72053087192</v>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+46,2%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45912.76786456561</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Pardubi</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HC Pardubice – BK Mlada BoleslavExtraliga</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>14/09 15:00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+45,0%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45912.76786456561</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | HC Sotchi </t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HC Sotchi – Traktor TcheliabinskRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+42,6%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45912.76786456561</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | HC Spartak</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HC Spartak Moscou – Torpedo Nijni NovgorodRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+41,2%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45912.76786456561</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | HC Barys –</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HC Barys – Dinamo MinskRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>13/09 12:00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+40,7%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45912.76786456561</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | AL Nassr F</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AL Nassr FC – Al-KholoodSaudi Pro League</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>14/09 18:00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+40,3%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45912.76786456561</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KalPa – Ta</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>KalPa – Tappara TampereFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>13/09 14:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+39,6%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45912.76786456561</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Rapid Buca</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Rapid Bucarest – FC HermannstadtLiga 1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>21/09 18:00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+39,2%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45912.76786456561</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | SKA Saint </t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SKA Saint Pétersbourg – HC Lada TogliattiRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+36,9%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45912.76786456561</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Sarmien</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CA Sarmiento – CA AldosiviLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>14/09 00:15</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+36,6%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45912.76786456561</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Godoy Cruz – Instituto AC CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>21/09 19:45</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+36,3%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45912.76786456561</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | AK Bars Ka</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AK Bars Kazan – Metallurg MagnitogorskRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+35,7%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45912.76786456561</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | Karlovy Va</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Karlovy Vary – HC OlomoucRép.Tchèque - Extraliga</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+35,5%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>45912.76786456561</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3472,10 +3472,8 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>100</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3488,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
       </c>
     </row>
     <row r="72">
@@ -3517,10 +3515,8 @@
           <t>14/09 15:00</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>110</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3533,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
       </c>
     </row>
     <row r="73">
@@ -3562,10 +3558,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F73" t="n">
+        <v>101</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3578,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
       </c>
     </row>
     <row r="74">
@@ -3607,10 +3601,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>101</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3623,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
       </c>
     </row>
     <row r="75">
@@ -3652,10 +3644,8 @@
           <t>13/09 12:00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>101</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3668,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
       </c>
     </row>
     <row r="76">
@@ -3697,10 +3687,8 @@
           <t>14/09 18:00</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>60</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3713,7 +3701,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
       </c>
     </row>
     <row r="77">
@@ -3742,10 +3730,8 @@
           <t>13/09 14:00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>100</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3758,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
       </c>
     </row>
     <row r="78">
@@ -3787,10 +3773,8 @@
           <t>21/09 18:00</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F78" t="n">
+        <v>55</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3803,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
       </c>
     </row>
     <row r="79">
@@ -3832,10 +3816,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F79" t="n">
+        <v>90</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3848,7 +3830,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
       </c>
     </row>
     <row r="80">
@@ -3877,10 +3859,8 @@
           <t>14/09 00:15</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F80" t="n">
+        <v>60</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3893,7 +3873,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
       </c>
     </row>
     <row r="81">
@@ -3922,10 +3902,8 @@
           <t>21/09 19:45</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F81" t="n">
+        <v>60</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3938,7 +3916,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
       </c>
     </row>
     <row r="82">
@@ -3967,10 +3945,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F82" t="n">
+        <v>90</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3983,7 +3959,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
       </c>
     </row>
     <row r="83">
@@ -4012,10 +3988,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>94.00</t>
-        </is>
+      <c r="F83" t="n">
+        <v>94</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4028,7 +4002,277 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45912.76786456561</v>
+        <v>45912.76786456018</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Pardubice </t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Pardubice – Mlada BoleslavRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>14/09 15:00</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>45912.80318565661</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kometa Brn</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Kometa Brno – Sparta PragueRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>14/09 14:30</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>+48,2%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>45912.80318565661</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Trinec – L</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Trinec – LiberecRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>14/09 15:00</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>+46,2%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>45912.80318565661</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Karlovy Va</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Karlovy Vary – OlomoucRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>+45,6%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>45912.80318565661</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Plzen – Ce</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Plzen – Ceske BudejoviceRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>14/09 14:30</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>97.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>+43,0%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>45912.80318565661</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kladno – M</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Kladno – Mountfield HKRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>93.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>+37,9%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>45912.80318565661</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4031,10 +4031,8 @@
           <t>14/09 15:00</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F84" t="n">
+        <v>140</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4047,7 +4045,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45912.80318565661</v>
+        <v>45912.80318565972</v>
       </c>
     </row>
     <row r="85">
@@ -4076,10 +4074,8 @@
           <t>14/09 14:30</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F85" t="n">
+        <v>100</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4092,7 +4088,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45912.80318565661</v>
+        <v>45912.80318565972</v>
       </c>
     </row>
     <row r="86">
@@ -4121,10 +4117,8 @@
           <t>14/09 15:00</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F86" t="n">
+        <v>100</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4137,7 +4131,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45912.80318565661</v>
+        <v>45912.80318565972</v>
       </c>
     </row>
     <row r="87">
@@ -4166,10 +4160,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F87" t="n">
+        <v>100</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4182,7 +4174,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>45912.80318565661</v>
+        <v>45912.80318565972</v>
       </c>
     </row>
     <row r="88">
@@ -4211,10 +4203,8 @@
           <t>14/09 14:30</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>97.00</t>
-        </is>
+      <c r="F88" t="n">
+        <v>97</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4227,7 +4217,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45912.80318565661</v>
+        <v>45912.80318565972</v>
       </c>
     </row>
     <row r="89">
@@ -4256,10 +4246,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>93.00</t>
-        </is>
+      <c r="F89" t="n">
+        <v>93</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4272,7 +4260,367 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>45912.80318565661</v>
+        <v>45912.80318565972</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | TPS – Lukk</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>TPS – LukkoFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>13/09 14:00</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>+76,1%</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>45912.84878048197</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KooKoo – S</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>KooKoo – SaiPaFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>13/09 14:00</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>+69,2%</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>45912.84878048197</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Fribour</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>HC Fribourg-Gotteron – EHC BielNational League A</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>13/09 17:45</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>+57,2%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>45912.84878048197</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Pelicans L</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Pelicans Lahti – HIFKFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>13/09 14:00</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>+54,8%</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>45912.84878048197</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Kiekko-Esp</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Kiekko-Espoo – Assat PoriLiiga</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>13/09 14:00</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>+52,4%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>45912.84878048197</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Cork City </t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Cork City – Shamrock RoversPremier Division</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>19/09 18:45</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>+52,2%</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>45912.84878048197</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Litvinov –</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Litvinov – VitkoviceRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>14/09 15:30</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>+50,9%</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>45912.84878048197</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Hameenlinn</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Hameenlinna – Vaasan SportLiiga</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>13/09 14:00</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>+50,6%</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>45912.84878048197</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4289,10 +4289,8 @@
           <t>13/09 14:00</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F90" t="n">
+        <v>125</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4305,7 +4303,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>45912.84878048197</v>
+        <v>45912.84878048611</v>
       </c>
     </row>
     <row r="91">
@@ -4334,10 +4332,8 @@
           <t>13/09 14:00</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F91" t="n">
+        <v>125</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4350,7 +4346,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>45912.84878048197</v>
+        <v>45912.84878048611</v>
       </c>
     </row>
     <row r="92">
@@ -4379,10 +4375,8 @@
           <t>13/09 17:45</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F92" t="n">
+        <v>100</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4395,7 +4389,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>45912.84878048197</v>
+        <v>45912.84878048611</v>
       </c>
     </row>
     <row r="93">
@@ -4424,10 +4418,8 @@
           <t>13/09 14:00</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F93" t="n">
+        <v>110</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4440,7 +4432,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>45912.84878048197</v>
+        <v>45912.84878048611</v>
       </c>
     </row>
     <row r="94">
@@ -4469,10 +4461,8 @@
           <t>13/09 14:00</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F94" t="n">
+        <v>110</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4485,7 +4475,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>45912.84878048197</v>
+        <v>45912.84878048611</v>
       </c>
     </row>
     <row r="95">
@@ -4514,10 +4504,8 @@
           <t>19/09 18:45</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F95" t="n">
+        <v>60</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4530,7 +4518,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>45912.84878048197</v>
+        <v>45912.84878048611</v>
       </c>
     </row>
     <row r="96">
@@ -4559,10 +4547,8 @@
           <t>14/09 15:30</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F96" t="n">
+        <v>100</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4575,7 +4561,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>45912.84878048197</v>
+        <v>45912.84878048611</v>
       </c>
     </row>
     <row r="97">
@@ -4604,10 +4590,8 @@
           <t>13/09 14:00</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F97" t="n">
+        <v>100</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4620,7 +4604,367 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>45912.84878048197</v>
+        <v>45912.84878048611</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Presov – B</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Presov – Banska BystricaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>+190%</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>45912.88709989136</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | HC Pustert</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>HC Pustertal – Graz 99ersAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>14/09 15:00</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>+138%</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>45912.88709989136</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Spisska No</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Spisska Nova Ves – Slovan Bratislava385076e7 Slovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>+134%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>45912.88709989136</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Nitra – Tr</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Nitra – TrencinSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>14/09 15:00</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>+98,7%</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>45912.88709989136</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HK Poprad </t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>HK Poprad – Dukla MichalovceExtraliga</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1,30%</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>+95,0%</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>45912.88709989136</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | TPS Turku </t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TPS Turku – Lukko RaumaLiiga</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>13/09 14:00</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>+86,4%</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>45912.88709989136</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | KooKoo – S</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>KooKoo – SaiPaLiiga</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>13/09 14:00</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>+84,6%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>45912.88709989136</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HKM AS Zvo</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>HKM AS Zvolen – MSHK ZilinaExtraliga</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>14/09 15:00</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>+69,2%</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>45912.88709989136</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4633,10 +4633,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F98" t="n">
+        <v>225</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4649,7 +4647,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>45912.88709989136</v>
+        <v>45912.88709989583</v>
       </c>
     </row>
     <row r="99">
@@ -4678,10 +4676,8 @@
           <t>14/09 15:00</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F99" t="n">
+        <v>200</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4694,7 +4690,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>45912.88709989136</v>
+        <v>45912.88709989583</v>
       </c>
     </row>
     <row r="100">
@@ -4723,10 +4719,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F100" t="n">
+        <v>175</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4739,7 +4733,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>45912.88709989136</v>
+        <v>45912.88709989583</v>
       </c>
     </row>
     <row r="101">
@@ -4768,10 +4762,8 @@
           <t>14/09 15:00</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F101" t="n">
+        <v>150</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4784,7 +4776,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>45912.88709989136</v>
+        <v>45912.88709989583</v>
       </c>
     </row>
     <row r="102">
@@ -4813,10 +4805,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F102" t="n">
+        <v>150</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4829,7 +4819,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>45912.88709989136</v>
+        <v>45912.88709989583</v>
       </c>
     </row>
     <row r="103">
@@ -4858,10 +4848,8 @@
           <t>13/09 14:00</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F103" t="n">
+        <v>125</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4874,7 +4862,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>45912.88709989136</v>
+        <v>45912.88709989583</v>
       </c>
     </row>
     <row r="104">
@@ -4903,10 +4891,8 @@
           <t>13/09 14:00</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F104" t="n">
+        <v>125</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4919,7 +4905,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>45912.88709989136</v>
+        <v>45912.88709989583</v>
       </c>
     </row>
     <row r="105">
@@ -4948,23 +4934,426 @@
           <t>14/09 15:00</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" t="n">
+        <v>125</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>+69,2%</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>45912.88709989583</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Wolfsburg </t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Wolfsburg Grizzly – Nurnberg Ice TigersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>14/09 14:30</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>+202%</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>45912.92957753457</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Pustertal </t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Pustertal Wolfe – MM Graz 99ersICE</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>14/09 15:00</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>+178%</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>45912.92957753457</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Augsburger</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Augsburger Panther – Adler MannheimAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>14/09 14:30</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>+173%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>45912.92957753457</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Dresdner –</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Dresdner – IngolstadtAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>14/09 12:00</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>+145%</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>45912.92957753457</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Poprad – M</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Poprad – MichalovceSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>+142%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>45912.92957753457</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Iserlohn R</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Iserlohn Roosters – Schwenninger Wild WingsAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>14/09 14:30</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>+111%</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>45912.92957753457</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Straubing </t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Straubing Tigers – Löwen FrankfurtAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>14/09 17:00</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>+108%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>45912.92957753457</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Zvolen – Z</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Zvolen – ZilinaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>14/09 15:00</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>+69,2%</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>45912.88709989136</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>+72,2%</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>45912.92957753457</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kosice – L</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Kosice – Liptovsky MikulasSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>14/09 14:00</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>+67,3%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>45912.92957753457</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-12.xlsx
+++ b/data/valuebets_database_2025-09-12.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4977,10 +4977,8 @@
           <t>14/09 14:30</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F106" t="n">
+        <v>225</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4993,7 +4991,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>45912.92957753457</v>
+        <v>45912.92957753472</v>
       </c>
     </row>
     <row r="107">
@@ -5022,10 +5020,8 @@
           <t>14/09 15:00</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F107" t="n">
+        <v>200</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5038,7 +5034,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>45912.92957753457</v>
+        <v>45912.92957753472</v>
       </c>
     </row>
     <row r="108">
@@ -5067,10 +5063,8 @@
           <t>14/09 14:30</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F108" t="n">
+        <v>200</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5083,7 +5077,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>45912.92957753457</v>
+        <v>45912.92957753472</v>
       </c>
     </row>
     <row r="109">
@@ -5112,10 +5106,8 @@
           <t>14/09 12:00</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F109" t="n">
+        <v>175</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5128,7 +5120,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>45912.92957753457</v>
+        <v>45912.92957753472</v>
       </c>
     </row>
     <row r="110">
@@ -5157,10 +5149,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F110" t="n">
+        <v>175</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5173,7 +5163,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>45912.92957753457</v>
+        <v>45912.92957753472</v>
       </c>
     </row>
     <row r="111">
@@ -5202,10 +5192,8 @@
           <t>14/09 14:30</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F111" t="n">
+        <v>150</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5218,7 +5206,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>45912.92957753457</v>
+        <v>45912.92957753472</v>
       </c>
     </row>
     <row r="112">
@@ -5247,10 +5235,8 @@
           <t>14/09 17:00</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F112" t="n">
+        <v>150</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5263,7 +5249,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>45912.92957753457</v>
+        <v>45912.92957753472</v>
       </c>
     </row>
     <row r="113">
@@ -5292,10 +5278,8 @@
           <t>14/09 15:00</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F113" t="n">
+        <v>125</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5308,7 +5292,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>45912.92957753457</v>
+        <v>45912.92957753472</v>
       </c>
     </row>
     <row r="114">
@@ -5337,10 +5321,8 @@
           <t>14/09 14:00</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F114" t="n">
+        <v>125</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5353,7 +5335,97 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>45912.92957753457</v>
+        <v>45912.92957753472</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Dresdner E</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Dresdner Eislowen – ERC IngolstadtDEL</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>14/09 12:00</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>+153%</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>45912.9709139853</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Iserlohn –</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Iserlohn – Wild WingsDEL</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>14/09 14:30</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>+104%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>45912.9709139853</v>
       </c>
     </row>
   </sheetData>
